--- a/12600438.xlsx
+++ b/12600438.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\python minor proj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DC7ACA-B163-48A4-959E-DBDA27EC98D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7D1404-8EC4-4A82-BFA9-D4947871A0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -547,9 +547,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -568,6 +565,9 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -575,23 +575,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
         <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1065,49 +1053,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="21">
         <v>12600438</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
@@ -1117,22 +1105,22 @@
       <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1179,2738 +1167,2810 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
+      <c r="A6" s="13">
         <v>46247</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="14">
         <v>420</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="14">
         <v>120</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="14">
         <v>150</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="14">
         <v>60</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="14">
         <v>250</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="14">
         <v>5</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="14">
         <v>30</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="15">
         <f t="shared" ref="I6:I63" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1030</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="15">
         <f t="shared" ref="J6:J63" si="1">IF(I6="","",1440-I6)</f>
         <v>410</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="19" t="s">
+      <c r="M6" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N6" s="20" t="s">
+      <c r="N6" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="16">
+      <c r="A7" s="13">
         <v>46248</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="14">
         <v>330</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="14">
         <v>60</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="14">
         <v>135</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="14">
         <v>30</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="14">
         <v>300</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="14">
         <v>6</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="14">
         <v>105</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="19" t="s">
+      <c r="M7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N7" s="20" t="s">
+      <c r="N7" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="16">
+      <c r="A8" s="13">
         <v>46249</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="14">
         <v>540</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="14">
         <v>120</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="14">
         <v>240</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="14">
         <v>60</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="14">
         <v>0</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="14">
         <v>0</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="14">
         <v>150</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
         <v>330</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="16" t="s">
         <v>55</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="16">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
         <v>46250</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="14">
         <v>540</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="14">
         <v>120</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="14">
         <v>300</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="14">
         <v>60</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="14">
         <v>0</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="14">
         <v>0</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="14">
         <v>180</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="16" t="s">
         <v>55</v>
       </c>
       <c r="N9" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="16">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
         <v>46251</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="14">
         <v>420</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="14">
         <v>60</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="14">
         <v>120</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="14">
         <v>75</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="14">
         <v>350</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="14">
         <v>7</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="14">
         <v>30</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
         <v>1055</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
         <v>385</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="20" t="s">
+      <c r="N10" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="16">
+      <c r="A11" s="13">
         <v>46252</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="14">
         <v>360</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="14">
         <v>75</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="14">
         <v>135</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="14">
         <v>50</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="14">
         <v>250</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="14">
         <v>5</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="14">
         <v>75</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
         <v>945</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
         <v>495</v>
       </c>
-      <c r="K11" s="19" t="s">
+      <c r="K11" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="19" t="s">
+      <c r="M11" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N11" s="20" t="s">
+      <c r="N11" s="17" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="16">
+      <c r="A12" s="13">
         <v>46253</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="14">
         <v>420</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="14">
         <v>120</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="14">
         <v>150</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="14">
         <v>90</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="14">
         <v>200</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="14">
         <v>4</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="14">
         <v>30</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
         <v>1010</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
         <v>430</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M12" s="19" t="s">
+      <c r="M12" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="N12" s="18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="16">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
         <v>46254</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="14">
         <v>360</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="14">
         <v>45</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="14">
         <v>105</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="14">
         <v>45</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="14">
         <v>250</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="14">
         <v>5</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="14">
         <v>60</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
         <v>865</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
         <v>575</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="K13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="20" t="s">
+      <c r="N13" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="16">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
         <v>46255</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="14">
         <v>330</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="14">
         <v>75</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="14">
         <v>150</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="14">
         <v>40</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="14">
         <v>300</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="14">
         <v>6</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="14">
         <v>75</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
         <v>970</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
         <v>470</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="19" t="s">
+      <c r="L14" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N14" s="20" t="s">
+      <c r="N14" s="17" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="16">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
         <v>46256</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="14">
         <v>540</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="14">
         <v>120</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="14">
         <v>360</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="14">
         <v>80</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="14">
         <v>0</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="14">
         <v>0</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="14">
         <v>100</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K15" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L15" s="19" t="s">
+      <c r="L15" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N15" s="20" t="s">
+      <c r="N15" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="16">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
         <v>46257</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="14">
         <v>540</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="14">
         <v>0</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="14">
         <v>300</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="14">
         <v>60</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="14">
         <v>0</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="14">
         <v>0</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="14">
         <v>30</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
         <v>930</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
         <v>510</v>
       </c>
-      <c r="K16" s="19" t="s">
+      <c r="K16" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L16" s="19" t="s">
+      <c r="L16" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="19" t="s">
+      <c r="M16" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N16" s="20" t="s">
+      <c r="N16" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="16">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
         <v>46258</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="14">
         <v>420</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="14">
         <v>60</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="14">
         <v>150</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="14">
         <v>75</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="14">
         <v>350</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="14">
         <v>7</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="14">
         <v>30</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
         <v>1085</v>
       </c>
-      <c r="J17" s="18">
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
         <v>355</v>
       </c>
-      <c r="K17" s="19" t="s">
+      <c r="K17" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L17" s="19" t="s">
+      <c r="L17" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="19" t="s">
+      <c r="M17" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N17" s="20" t="s">
+      <c r="N17" s="17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="16">
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
         <v>46259</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="14">
         <v>360</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="14">
         <v>120</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="14">
         <v>120</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="14">
         <v>45</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="14">
         <v>250</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="14">
         <v>5</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="14">
         <v>30</v>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
         <v>925</v>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
         <v>515</v>
       </c>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L18" s="19" t="s">
+      <c r="L18" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M18" s="19" t="s">
+      <c r="M18" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="20" t="s">
+      <c r="N18" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="16">
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
         <v>46260</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="14">
         <v>300</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="14">
         <v>60</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="14">
         <v>150</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="14">
         <v>40</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="14">
         <v>200</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="14">
         <v>4</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="14">
         <v>45</v>
       </c>
-      <c r="I19" s="18">
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
         <v>795</v>
       </c>
-      <c r="J19" s="18">
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
         <v>645</v>
       </c>
-      <c r="K19" s="19" t="s">
+      <c r="K19" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L19" s="19" t="s">
+      <c r="L19" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M19" s="19" t="s">
+      <c r="M19" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N19" s="20" t="s">
+      <c r="N19" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="16">
+      <c r="A20" s="13">
         <v>46261</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="14">
         <v>330</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="14">
         <v>75</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="14">
         <v>150</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="14">
         <v>30</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="14">
         <v>250</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="14">
         <v>5</v>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="14">
         <v>45</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
         <v>880</v>
       </c>
-      <c r="J20" s="18">
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
         <v>560</v>
       </c>
-      <c r="K20" s="19" t="s">
+      <c r="K20" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L20" s="19" t="s">
+      <c r="L20" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N20" s="20" t="s">
+      <c r="N20" s="17" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="16">
+      <c r="A21" s="13">
         <v>46262</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="14">
         <v>420</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="14">
         <v>60</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="14">
         <v>150</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="14">
         <v>90</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="14">
         <v>300</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="14">
         <v>6</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="14">
         <v>105</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
         <v>1125</v>
       </c>
-      <c r="J21" s="18">
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
         <v>315</v>
       </c>
-      <c r="K21" s="19" t="s">
+      <c r="K21" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L21" s="19" t="s">
+      <c r="L21" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M21" s="19" t="s">
+      <c r="M21" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N21" s="20" t="s">
+      <c r="N21" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="16">
+      <c r="A22" s="13">
         <v>46263</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="14">
         <v>540</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="14">
         <v>20</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="14">
         <v>260</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="14">
         <v>60</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="14">
         <v>0</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="14">
         <v>0</v>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="14">
         <v>30</v>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
         <v>910</v>
       </c>
-      <c r="J22" s="18">
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
         <v>530</v>
       </c>
-      <c r="K22" s="19" t="s">
+      <c r="K22" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M22" s="19" t="s">
+      <c r="M22" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N22" s="20" t="s">
+      <c r="N22" s="17" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="16">
+      <c r="A23" s="13">
         <v>46264</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="14">
         <v>540</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="14">
         <v>40</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="14">
         <v>240</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="14">
         <v>120</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="14">
         <v>0</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="14">
         <v>0</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="14">
         <v>10</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
         <v>950</v>
       </c>
-      <c r="J23" s="18">
+      <c r="J23" s="15">
         <f>IF(I23="","",1440-I23)</f>
         <v>490</v>
       </c>
-      <c r="K23" s="19" t="s">
+      <c r="K23" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M23" s="19" t="s">
+      <c r="M23" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N23" s="20" t="s">
+      <c r="N23" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="16">
+      <c r="A24" s="13">
         <v>46265</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="14">
         <v>360</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="14">
         <v>75</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="14">
         <v>135</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="14">
         <v>55</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="14">
         <v>350</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="14">
         <v>7</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="14">
         <v>75</v>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="K24" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N24" s="20" t="s">
+      <c r="N24" s="17" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="16">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
         <v>46266</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="14">
         <v>330</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="14">
         <v>60</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="14">
         <v>120</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="14">
         <v>40</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="14">
         <v>250</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="14">
         <v>5</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="14">
         <v>60</v>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
         <v>860</v>
       </c>
-      <c r="J25" s="18">
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="K25" s="19" t="s">
+      <c r="K25" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M25" s="19" t="s">
+      <c r="M25" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N25" s="20" t="s">
+      <c r="N25" s="17" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="16">
+      <c r="A26" s="13">
         <v>46267</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="14">
         <v>360</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="14">
         <v>75</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="14">
         <v>150</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="14">
         <v>50</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="14">
         <v>200</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="14">
         <v>4</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="14">
         <v>45</v>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
         <v>880</v>
       </c>
-      <c r="J26" s="18">
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
         <v>560</v>
       </c>
-      <c r="K26" s="19" t="s">
+      <c r="K26" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L26" s="19" t="s">
+      <c r="L26" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M26" s="19" t="s">
+      <c r="M26" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="20" t="s">
+      <c r="N26" s="17" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="16">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
         <v>46268</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="14">
         <v>420</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="14">
         <v>60</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="14">
         <v>135</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="14">
         <v>75</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="14">
         <v>250</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="14">
         <v>5</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="14">
         <v>45</v>
       </c>
-      <c r="I27" s="18">
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
         <v>985</v>
       </c>
-      <c r="J27" s="18">
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
         <v>455</v>
       </c>
-      <c r="K27" s="19" t="s">
+      <c r="K27" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L27" s="19" t="s">
+      <c r="L27" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M27" s="19" t="s">
+      <c r="M27" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N27" s="20" t="s">
+      <c r="N27" s="17" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="16">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
         <v>46269</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="14">
         <v>330</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="14">
         <v>75</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="14">
         <v>150</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="14">
         <v>30</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="14">
         <v>300</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="14">
         <v>6</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="14">
         <v>30</v>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
         <v>915</v>
       </c>
-      <c r="J28" s="18">
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
         <v>525</v>
       </c>
-      <c r="K28" s="19" t="s">
+      <c r="K28" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L28" s="19" t="s">
+      <c r="L28" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M28" s="19" t="s">
+      <c r="M28" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N28" s="20" t="s">
+      <c r="N28" s="17" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="16">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
         <v>46270</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="14">
         <v>540</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="14">
         <v>120</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="14">
         <v>180</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="14">
         <v>80</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="14">
         <v>0</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="14">
         <v>0</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="14">
         <v>180</v>
       </c>
-      <c r="I29" s="18">
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="J29" s="18">
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
         <v>340</v>
       </c>
-      <c r="K29" s="19" t="s">
+      <c r="K29" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L29" s="19" t="s">
+      <c r="L29" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M29" s="19" t="s">
+      <c r="M29" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N29" s="20" t="s">
+      <c r="N29" s="17" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="16">
+      <c r="A30" s="13">
         <v>46271</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="14">
         <v>540</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="14">
         <v>10</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="14">
         <v>150</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="14">
         <v>90</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="14">
         <v>0</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="14">
         <v>0</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="14">
         <v>120</v>
       </c>
-      <c r="I30" s="18">
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
         <v>910</v>
       </c>
-      <c r="J30" s="18">
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
         <v>530</v>
       </c>
-      <c r="K30" s="19" t="s">
+      <c r="K30" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L30" s="19" t="s">
+      <c r="L30" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M30" s="19" t="s">
+      <c r="M30" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N30" s="20" t="s">
+      <c r="N30" s="17" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="16">
+      <c r="A31" s="13">
         <v>46272</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="14">
         <v>360</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="14">
         <v>60</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="14">
         <v>135</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="14">
         <v>45</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="14">
         <v>350</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="14">
         <v>7</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="14">
         <v>45</v>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
         <v>995</v>
       </c>
-      <c r="J31" s="18">
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
         <v>445</v>
       </c>
-      <c r="K31" s="19" t="s">
+      <c r="K31" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L31" s="19" t="s">
+      <c r="L31" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M31" s="19" t="s">
+      <c r="M31" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N31" s="20" t="s">
+      <c r="N31" s="17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="16">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
         <v>46273</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="14">
         <v>330</v>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="14">
         <v>75</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="14">
         <v>120</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="14">
         <v>30</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="14">
         <v>250</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="14">
         <v>4</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="14">
         <v>75</v>
       </c>
-      <c r="I32" s="18">
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
         <v>880</v>
       </c>
-      <c r="J32" s="18">
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
         <v>560</v>
       </c>
-      <c r="K32" s="19" t="s">
+      <c r="K32" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L32" s="19" t="s">
+      <c r="L32" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M32" s="19" t="s">
+      <c r="M32" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N32" s="20" t="s">
+      <c r="N32" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="16">
+      <c r="A33" s="13">
         <v>46274</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="14">
         <v>420</v>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="14">
         <v>60</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="14">
         <v>150</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="14">
         <v>80</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="14">
         <v>200</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="14">
         <v>4</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="14">
         <v>60</v>
       </c>
-      <c r="I33" s="18">
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
         <v>970</v>
       </c>
-      <c r="J33" s="18">
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
         <v>470</v>
       </c>
-      <c r="K33" s="19" t="s">
+      <c r="K33" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L33" s="19" t="s">
+      <c r="L33" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M33" s="19" t="s">
+      <c r="M33" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N33" s="20" t="s">
+      <c r="N33" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="16">
+      <c r="A34" s="13">
         <v>46275</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="14">
         <v>360</v>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="14">
         <v>75</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="14">
         <v>180</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="14">
         <v>50</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="14">
         <v>250</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="14">
         <v>5</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="14">
         <v>45</v>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="J34" s="18">
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K34" s="19" t="s">
+      <c r="K34" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L34" s="19" t="s">
+      <c r="L34" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M34" s="19" t="s">
+      <c r="M34" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N34" s="20" t="s">
+      <c r="N34" s="17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="16">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
         <v>46276</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="14">
         <v>300</v>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="14">
         <v>60</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="14">
         <v>180</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="14">
         <v>45</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="14">
         <v>300</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="14">
         <v>6</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="14">
         <v>135</v>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="J35" s="18">
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K35" s="19" t="s">
+      <c r="K35" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L35" s="19" t="s">
+      <c r="L35" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M35" s="19" t="s">
+      <c r="M35" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N35" s="20" t="s">
+      <c r="N35" s="17" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="16">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
         <v>46277</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="14">
         <v>300</v>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="14">
         <v>210</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="14">
         <v>0</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="14">
         <v>0</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="14">
         <v>0</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="14">
         <v>0</v>
       </c>
-      <c r="H36" s="17">
+      <c r="H36" s="14">
         <v>360</v>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
         <v>870</v>
       </c>
-      <c r="J36" s="18">
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
         <v>570</v>
       </c>
-      <c r="K36" s="19" t="s">
+      <c r="K36" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L36" s="19" t="s">
+      <c r="L36" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M36" s="19" t="s">
+      <c r="M36" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N36" s="20" t="s">
+      <c r="N36" s="17" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="16">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
         <v>46278</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="14">
         <v>540</v>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="14">
         <v>150</v>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="14">
         <v>0</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="14">
         <v>0</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="14">
         <v>0</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="14">
         <v>0</v>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="14">
         <v>480</v>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
         <v>1170</v>
       </c>
-      <c r="J37" s="18">
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
         <v>270</v>
       </c>
-      <c r="K37" s="19" t="s">
+      <c r="K37" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L37" s="19" t="s">
+      <c r="L37" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M37" s="19" t="s">
+      <c r="M37" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N37" s="20" t="s">
+      <c r="N37" s="17" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="16">
+      <c r="A38" s="13">
         <v>46279</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="14">
         <v>330</v>
       </c>
-      <c r="C38" s="17">
+      <c r="C38" s="14">
         <v>75</v>
       </c>
-      <c r="D38" s="17">
+      <c r="D38" s="14">
         <v>150</v>
       </c>
-      <c r="E38" s="17">
+      <c r="E38" s="14">
         <v>40</v>
       </c>
-      <c r="F38" s="17">
+      <c r="F38" s="14">
         <v>350</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="14">
         <v>7</v>
       </c>
-      <c r="H38" s="17">
+      <c r="H38" s="14">
         <v>30</v>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
         <v>975</v>
       </c>
-      <c r="J38" s="18">
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
         <v>465</v>
       </c>
-      <c r="K38" s="19" t="s">
+      <c r="K38" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L38" s="19" t="s">
+      <c r="L38" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M38" s="19" t="s">
+      <c r="M38" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N38" s="20" t="s">
+      <c r="N38" s="17" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="16">
+      <c r="A39" s="13">
         <v>46280</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="14">
         <v>360</v>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="14">
         <v>60</v>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="14">
         <v>150</v>
       </c>
-      <c r="E39" s="17">
+      <c r="E39" s="14">
         <v>45</v>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="14">
         <v>250</v>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="14">
         <v>5</v>
       </c>
-      <c r="H39" s="17">
+      <c r="H39" s="14">
         <v>75</v>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
         <v>940</v>
       </c>
-      <c r="J39" s="18">
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="K39" s="19" t="s">
+      <c r="K39" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L39" s="19" t="s">
+      <c r="L39" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M39" s="19" t="s">
+      <c r="M39" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N39" s="20" t="s">
+      <c r="N39" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="16">
+      <c r="A40" s="13">
         <v>46281</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="14">
         <v>330</v>
       </c>
-      <c r="C40" s="17">
+      <c r="C40" s="14">
         <v>75</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="14">
         <v>150</v>
       </c>
-      <c r="E40" s="17">
+      <c r="E40" s="14">
         <v>30</v>
       </c>
-      <c r="F40" s="17">
+      <c r="F40" s="14">
         <v>250</v>
       </c>
-      <c r="G40" s="17">
+      <c r="G40" s="14">
         <v>5</v>
       </c>
-      <c r="H40" s="17">
+      <c r="H40" s="14">
         <v>105</v>
       </c>
-      <c r="I40" s="18">
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
         <v>940</v>
       </c>
-      <c r="J40" s="18">
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="K40" s="19" t="s">
+      <c r="K40" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L40" s="19" t="s">
+      <c r="L40" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M40" s="19" t="s">
+      <c r="M40" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N40" s="20" t="s">
+      <c r="N40" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="16">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
         <v>46282</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="14">
         <v>360</v>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="14">
         <v>60</v>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="14">
         <v>240</v>
       </c>
-      <c r="E41" s="17">
+      <c r="E41" s="14">
         <v>50</v>
       </c>
-      <c r="F41" s="17">
+      <c r="F41" s="14">
         <v>250</v>
       </c>
-      <c r="G41" s="17">
+      <c r="G41" s="14">
         <v>5</v>
       </c>
-      <c r="H41" s="17">
+      <c r="H41" s="14">
         <v>30</v>
       </c>
-      <c r="I41" s="18">
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
         <v>990</v>
       </c>
-      <c r="J41" s="18">
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
-      <c r="K41" s="19" t="s">
+      <c r="K41" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L41" s="19" t="s">
+      <c r="L41" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M41" s="19" t="s">
+      <c r="M41" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N41" s="20" t="s">
+      <c r="N41" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="16">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
         <v>46283</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="14">
         <v>420</v>
       </c>
-      <c r="C42" s="17">
+      <c r="C42" s="14">
         <v>60</v>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="14">
         <v>150</v>
       </c>
-      <c r="E42" s="17">
+      <c r="E42" s="14">
         <v>105</v>
       </c>
-      <c r="F42" s="17">
+      <c r="F42" s="14">
         <v>300</v>
       </c>
-      <c r="G42" s="17">
+      <c r="G42" s="14">
         <v>6</v>
       </c>
-      <c r="H42" s="17">
+      <c r="H42" s="14">
         <v>45</v>
       </c>
-      <c r="I42" s="18">
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="J42" s="18">
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
-      <c r="K42" s="19" t="s">
+      <c r="K42" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L42" s="19" t="s">
+      <c r="L42" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M42" s="19" t="s">
+      <c r="M42" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N42" s="20" t="s">
+      <c r="N42" s="17" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="16">
+      <c r="A43" s="13">
         <v>46284</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="14">
         <v>420</v>
       </c>
-      <c r="C43" s="17">
+      <c r="C43" s="14">
         <v>60</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="14">
         <v>180</v>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="14">
         <v>90</v>
       </c>
-      <c r="F43" s="17">
+      <c r="F43" s="14">
         <v>50</v>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="14">
         <v>1</v>
       </c>
-      <c r="H43" s="17">
+      <c r="H43" s="14">
         <v>150</v>
       </c>
-      <c r="I43" s="18">
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
         <v>950</v>
       </c>
-      <c r="J43" s="18">
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
         <v>490</v>
       </c>
-      <c r="K43" s="19" t="s">
+      <c r="K43" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L43" s="19" t="s">
+      <c r="L43" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M43" s="19" t="s">
+      <c r="M43" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N43" s="20" t="s">
+      <c r="N43" s="17" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="16">
+      <c r="A44" s="13">
         <v>46285</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="14">
         <v>540</v>
       </c>
-      <c r="C44" s="17">
+      <c r="C44" s="14">
         <v>10</v>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="14">
         <v>180</v>
       </c>
-      <c r="E44" s="17">
+      <c r="E44" s="14">
         <v>120</v>
       </c>
-      <c r="F44" s="17">
+      <c r="F44" s="14">
         <v>0</v>
       </c>
-      <c r="G44" s="17">
+      <c r="G44" s="14">
         <v>0</v>
       </c>
-      <c r="H44" s="17">
+      <c r="H44" s="14">
         <v>120</v>
       </c>
-      <c r="I44" s="18">
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
         <v>970</v>
       </c>
-      <c r="J44" s="18">
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
         <v>470</v>
       </c>
-      <c r="K44" s="19" t="s">
+      <c r="K44" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L44" s="19" t="s">
+      <c r="L44" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M44" s="19" t="s">
+      <c r="M44" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N44" s="20" t="s">
+      <c r="N44" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="16">
+      <c r="A45" s="13">
         <v>46286</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="14">
         <v>360</v>
       </c>
-      <c r="C45" s="17">
+      <c r="C45" s="14">
         <v>75</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="14">
         <v>240</v>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="14">
         <v>45</v>
       </c>
-      <c r="F45" s="17">
+      <c r="F45" s="14">
         <v>350</v>
       </c>
-      <c r="G45" s="17">
+      <c r="G45" s="14">
         <v>7</v>
       </c>
-      <c r="H45" s="17">
+      <c r="H45" s="14">
         <v>45</v>
       </c>
-      <c r="I45" s="18">
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
         <v>1115</v>
       </c>
-      <c r="J45" s="18">
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
-      <c r="K45" s="19" t="s">
+      <c r="K45" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L45" s="19" t="s">
+      <c r="L45" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M45" s="19" t="s">
+      <c r="M45" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N45" s="20" t="s">
+      <c r="N45" s="17" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="16">
+      <c r="A46" s="13">
         <v>46287</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="14">
         <v>420</v>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="14">
         <v>120</v>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="14">
         <v>240</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="14">
         <v>60</v>
       </c>
-      <c r="F46" s="17">
+      <c r="F46" s="14">
         <v>250</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="14">
         <v>5</v>
       </c>
-      <c r="H46" s="17">
+      <c r="H46" s="14">
         <v>30</v>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
         <v>1120</v>
       </c>
-      <c r="J46" s="18">
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
-      <c r="K46" s="19" t="s">
+      <c r="K46" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L46" s="19" t="s">
+      <c r="L46" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M46" s="19" t="s">
+      <c r="M46" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N46" s="20" t="s">
+      <c r="N46" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="16">
+      <c r="A47" s="13">
         <v>46288</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="14">
         <v>360</v>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="14">
         <v>45</v>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="14">
         <v>240</v>
       </c>
-      <c r="E47" s="17">
+      <c r="E47" s="14">
         <v>45</v>
       </c>
-      <c r="F47" s="17">
+      <c r="F47" s="14">
         <v>200</v>
       </c>
-      <c r="G47" s="17">
+      <c r="G47" s="14">
         <v>4</v>
       </c>
-      <c r="H47" s="17">
+      <c r="H47" s="14">
         <v>45</v>
       </c>
-      <c r="I47" s="18">
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
         <v>935</v>
       </c>
-      <c r="J47" s="18">
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
         <v>505</v>
       </c>
-      <c r="K47" s="19" t="s">
+      <c r="K47" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="L47" s="19" t="s">
+      <c r="L47" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M47" s="19" t="s">
+      <c r="M47" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N47" s="20" t="s">
+      <c r="N47" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="16">
+      <c r="A48" s="13">
         <v>46289</v>
       </c>
-      <c r="B48" s="17">
+      <c r="B48" s="14">
         <v>420</v>
       </c>
-      <c r="C48" s="17">
+      <c r="C48" s="14">
         <v>60</v>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="14">
         <v>240</v>
       </c>
-      <c r="E48" s="17">
+      <c r="E48" s="14">
         <v>60</v>
       </c>
-      <c r="F48" s="17">
+      <c r="F48" s="14">
         <v>250</v>
       </c>
-      <c r="G48" s="17">
+      <c r="G48" s="14">
         <v>5</v>
       </c>
-      <c r="H48" s="17">
+      <c r="H48" s="14">
         <v>60</v>
       </c>
-      <c r="I48" s="18">
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
         <v>1090</v>
       </c>
-      <c r="J48" s="18">
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
         <v>350</v>
       </c>
-      <c r="K48" s="19" t="s">
+      <c r="K48" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L48" s="19" t="s">
+      <c r="L48" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M48" s="19" t="s">
+      <c r="M48" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N48" s="20" t="s">
+      <c r="N48" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="16">
+      <c r="A49" s="13">
         <v>46290</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="14">
         <v>360</v>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="14">
         <v>120</v>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="14">
         <v>150</v>
       </c>
-      <c r="E49" s="17">
+      <c r="E49" s="14">
         <v>50</v>
       </c>
-      <c r="F49" s="17">
+      <c r="F49" s="14">
         <v>300</v>
       </c>
-      <c r="G49" s="17">
+      <c r="G49" s="14">
         <v>6</v>
       </c>
-      <c r="H49" s="17">
+      <c r="H49" s="14">
         <v>75</v>
       </c>
-      <c r="I49" s="18">
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
         <v>1055</v>
       </c>
-      <c r="J49" s="18">
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
         <v>385</v>
       </c>
-      <c r="K49" s="19" t="s">
+      <c r="K49" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L49" s="19" t="s">
+      <c r="L49" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M49" s="19" t="s">
+      <c r="M49" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N49" s="20" t="s">
+      <c r="N49" s="17" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="16">
+      <c r="A50" s="13">
         <v>46291</v>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="14">
         <v>540</v>
       </c>
-      <c r="C50" s="17">
+      <c r="C50" s="14">
         <v>30</v>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="14">
         <v>120</v>
       </c>
-      <c r="E50" s="17">
+      <c r="E50" s="14">
         <v>60</v>
       </c>
-      <c r="F50" s="17">
+      <c r="F50" s="14">
         <v>0</v>
       </c>
-      <c r="G50" s="17">
+      <c r="G50" s="14">
         <v>0</v>
       </c>
-      <c r="H50" s="17">
+      <c r="H50" s="14">
         <v>60</v>
       </c>
-      <c r="I50" s="18">
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
         <v>810</v>
       </c>
-      <c r="J50" s="18">
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
         <v>630</v>
       </c>
-      <c r="K50" s="19" t="s">
+      <c r="K50" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="L50" s="19" t="s">
+      <c r="L50" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M50" s="19" t="s">
+      <c r="M50" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N50" s="20" t="s">
+      <c r="N50" s="17" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="16">
+      <c r="A51" s="13">
         <v>46292</v>
       </c>
-      <c r="B51" s="17">
+      <c r="B51" s="14">
         <v>540</v>
       </c>
-      <c r="C51" s="17">
+      <c r="C51" s="14">
         <v>60</v>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="14">
         <v>120</v>
       </c>
-      <c r="E51" s="17">
+      <c r="E51" s="14">
         <v>75</v>
       </c>
-      <c r="F51" s="17">
+      <c r="F51" s="14">
         <v>0</v>
       </c>
-      <c r="G51" s="17">
+      <c r="G51" s="14">
         <v>0</v>
       </c>
-      <c r="H51" s="17">
+      <c r="H51" s="14">
         <v>45</v>
       </c>
-      <c r="I51" s="18">
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
         <v>840</v>
       </c>
-      <c r="J51" s="18">
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="K51" s="19" t="s">
+      <c r="K51" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L51" s="19" t="s">
+      <c r="L51" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M51" s="19" t="s">
+      <c r="M51" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N51" s="20" t="s">
+      <c r="N51" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="16">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="13">
         <v>46293</v>
       </c>
-      <c r="B52" s="17">
+      <c r="B52" s="14">
         <v>540</v>
       </c>
-      <c r="C52" s="17">
+      <c r="C52" s="14">
         <v>20</v>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="14">
         <v>100</v>
       </c>
-      <c r="E52" s="17">
+      <c r="E52" s="14">
         <v>0</v>
       </c>
-      <c r="F52" s="17">
+      <c r="F52" s="14">
         <v>0</v>
       </c>
-      <c r="G52" s="17">
+      <c r="G52" s="14">
         <v>0</v>
       </c>
-      <c r="H52" s="17">
+      <c r="H52" s="14">
         <v>120</v>
       </c>
-      <c r="I52" s="18">
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
         <v>780</v>
       </c>
-      <c r="J52" s="18">
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
         <v>660</v>
       </c>
-      <c r="K52" s="19" t="s">
+      <c r="K52" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L52" s="19" t="s">
+      <c r="L52" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="M52" s="19" t="s">
+      <c r="M52" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N52" s="20" t="s">
+      <c r="N52" s="17" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="16">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="13">
         <v>46294</v>
       </c>
-      <c r="B53" s="17">
+      <c r="B53" s="14">
         <v>300</v>
       </c>
-      <c r="C53" s="17">
+      <c r="C53" s="14">
         <v>0</v>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="14">
         <v>0</v>
       </c>
-      <c r="E53" s="17">
+      <c r="E53" s="14">
         <v>0</v>
       </c>
-      <c r="F53" s="17">
+      <c r="F53" s="14">
         <v>0</v>
       </c>
-      <c r="G53" s="17">
+      <c r="G53" s="14">
         <v>0</v>
       </c>
-      <c r="H53" s="17">
+      <c r="H53" s="14">
         <v>45</v>
       </c>
-      <c r="I53" s="18">
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
         <v>345</v>
       </c>
-      <c r="J53" s="18">
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
         <v>1095</v>
       </c>
-      <c r="K53" s="19" t="s">
+      <c r="K53" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L53" s="19" t="s">
+      <c r="L53" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="M53" s="19" t="s">
+      <c r="M53" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N53" s="20" t="s">
+      <c r="N53" s="17" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="16">
+      <c r="A54" s="13">
         <v>46295</v>
       </c>
-      <c r="B54" s="17">
+      <c r="B54" s="14">
         <v>300</v>
       </c>
-      <c r="C54" s="17">
+      <c r="C54" s="14">
         <v>0</v>
       </c>
-      <c r="D54" s="17">
+      <c r="D54" s="14">
         <v>0</v>
       </c>
-      <c r="E54" s="17">
+      <c r="E54" s="14">
         <v>0</v>
       </c>
-      <c r="F54" s="17">
+      <c r="F54" s="14">
         <v>0</v>
       </c>
-      <c r="G54" s="17">
+      <c r="G54" s="14">
         <v>0</v>
       </c>
-      <c r="H54" s="17">
+      <c r="H54" s="14">
         <v>120</v>
       </c>
-      <c r="I54" s="18">
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
         <v>420</v>
       </c>
-      <c r="J54" s="18">
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
         <v>1020</v>
       </c>
-      <c r="K54" s="19" t="s">
+      <c r="K54" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L54" s="19" t="s">
+      <c r="L54" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="M54" s="19" t="s">
+      <c r="M54" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N54" s="20" t="s">
+      <c r="N54" s="17" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="16">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="13">
         <v>46296</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="14">
         <v>420</v>
       </c>
-      <c r="C55" s="17">
+      <c r="C55" s="14">
         <v>0</v>
       </c>
-      <c r="D55" s="17">
+      <c r="D55" s="14">
         <v>30</v>
       </c>
-      <c r="E55" s="17">
+      <c r="E55" s="14">
         <v>0</v>
       </c>
-      <c r="F55" s="17">
+      <c r="F55" s="14">
         <v>0</v>
       </c>
-      <c r="G55" s="17">
+      <c r="G55" s="14">
         <v>0</v>
       </c>
-      <c r="H55" s="17">
+      <c r="H55" s="14">
         <v>180</v>
       </c>
-      <c r="I55" s="18">
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
         <v>630</v>
       </c>
-      <c r="J55" s="18">
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
         <v>810</v>
       </c>
-      <c r="K55" s="19" t="s">
+      <c r="K55" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L55" s="19" t="s">
+      <c r="L55" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="M55" s="19" t="s">
+      <c r="M55" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N55" s="20" t="s">
+      <c r="N55" s="17" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="16">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="13">
         <v>46297</v>
       </c>
-      <c r="B56" s="17">
+      <c r="B56" s="14">
         <v>540</v>
       </c>
-      <c r="C56" s="17">
+      <c r="C56" s="14">
         <v>120</v>
       </c>
-      <c r="D56" s="17">
+      <c r="D56" s="14">
         <v>120</v>
       </c>
-      <c r="E56" s="17">
+      <c r="E56" s="14">
         <v>60</v>
       </c>
-      <c r="F56" s="17">
+      <c r="F56" s="14">
         <v>0</v>
       </c>
-      <c r="G56" s="17">
+      <c r="G56" s="14">
         <v>0</v>
       </c>
-      <c r="H56" s="17">
+      <c r="H56" s="14">
         <v>150</v>
       </c>
-      <c r="I56" s="18">
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
         <v>990</v>
       </c>
-      <c r="J56" s="18">
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
-      <c r="K56" s="19" t="s">
+      <c r="K56" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L56" s="19" t="s">
+      <c r="L56" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M56" s="19" t="s">
+      <c r="M56" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N56" s="20" t="s">
+      <c r="N56" s="17" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="16">
+      <c r="A57" s="13">
         <v>46298</v>
       </c>
-      <c r="B57" s="17">
+      <c r="B57" s="14">
         <v>420</v>
       </c>
-      <c r="C57" s="17">
+      <c r="C57" s="14">
         <v>120</v>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="14">
         <v>120</v>
       </c>
-      <c r="E57" s="17">
+      <c r="E57" s="14">
         <v>60</v>
       </c>
-      <c r="F57" s="17">
+      <c r="F57" s="14">
         <v>0</v>
       </c>
-      <c r="G57" s="17">
+      <c r="G57" s="14">
         <v>0</v>
       </c>
-      <c r="H57" s="17">
+      <c r="H57" s="14">
         <v>180</v>
       </c>
-      <c r="I57" s="18">
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="J57" s="18">
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
         <v>540</v>
       </c>
-      <c r="K57" s="19" t="s">
+      <c r="K57" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L57" s="19" t="s">
+      <c r="L57" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M57" s="19" t="s">
+      <c r="M57" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N57" s="20" t="s">
+      <c r="N57" s="17" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="16">
+      <c r="A58" s="13">
         <v>46299</v>
       </c>
-      <c r="B58" s="17">
+      <c r="B58" s="14">
         <v>540</v>
       </c>
-      <c r="C58" s="17">
+      <c r="C58" s="14">
         <v>60</v>
       </c>
-      <c r="D58" s="17">
+      <c r="D58" s="14">
         <v>105</v>
       </c>
-      <c r="E58" s="17">
+      <c r="E58" s="14">
         <v>60</v>
       </c>
-      <c r="F58" s="17">
+      <c r="F58" s="14">
         <v>0</v>
       </c>
-      <c r="G58" s="17">
+      <c r="G58" s="14">
         <v>0</v>
       </c>
-      <c r="H58" s="17">
+      <c r="H58" s="14">
         <v>210</v>
       </c>
-      <c r="I58" s="18">
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
         <v>975</v>
       </c>
-      <c r="J58" s="18">
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
         <v>465</v>
       </c>
-      <c r="K58" s="19" t="s">
+      <c r="K58" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L58" s="19" t="s">
+      <c r="L58" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="M58" s="19" t="s">
+      <c r="M58" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N58" s="20" t="s">
+      <c r="N58" s="17" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="16">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="13">
         <v>46300</v>
       </c>
-      <c r="B59" s="17">
+      <c r="B59" s="14">
         <v>420</v>
       </c>
-      <c r="C59" s="17">
+      <c r="C59" s="14">
         <v>60</v>
       </c>
-      <c r="D59" s="17">
+      <c r="D59" s="14">
         <v>180</v>
       </c>
-      <c r="E59" s="17">
+      <c r="E59" s="14">
         <v>60</v>
       </c>
-      <c r="F59" s="17">
+      <c r="F59" s="14">
         <v>350</v>
       </c>
-      <c r="G59" s="17">
+      <c r="G59" s="14">
         <v>7</v>
       </c>
-      <c r="H59" s="17">
+      <c r="H59" s="14">
         <v>60</v>
       </c>
-      <c r="I59" s="18">
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
         <v>1130</v>
       </c>
-      <c r="J59" s="18">
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
         <v>310</v>
       </c>
-      <c r="K59" s="19" t="s">
+      <c r="K59" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L59" s="19" t="s">
+      <c r="L59" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M59" s="19" t="s">
+      <c r="M59" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N59" s="20" t="s">
+      <c r="N59" s="17" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="16">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="13">
         <v>46301</v>
       </c>
-      <c r="B60" s="17">
+      <c r="B60" s="14">
         <v>540</v>
       </c>
-      <c r="C60" s="17">
+      <c r="C60" s="14">
         <v>120</v>
       </c>
-      <c r="D60" s="17">
+      <c r="D60" s="14">
         <v>100</v>
       </c>
-      <c r="E60" s="17">
+      <c r="E60" s="14">
         <v>60</v>
       </c>
-      <c r="F60" s="17">
+      <c r="F60" s="14">
         <v>250</v>
       </c>
-      <c r="G60" s="17">
+      <c r="G60" s="14">
         <v>5</v>
       </c>
-      <c r="H60" s="17">
+      <c r="H60" s="14">
         <v>120</v>
       </c>
-      <c r="I60" s="18">
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
         <v>1190</v>
       </c>
-      <c r="J60" s="18">
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="K60" s="19" t="s">
+      <c r="K60" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L60" s="19" t="s">
+      <c r="L60" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="M60" s="19" t="s">
+      <c r="M60" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N60" s="20" t="s">
+      <c r="N60" s="17" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="16">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="13">
         <v>46302</v>
       </c>
-      <c r="B61" s="17">
+      <c r="B61" s="14">
         <v>540</v>
       </c>
-      <c r="C61" s="17">
+      <c r="C61" s="14">
         <v>60</v>
       </c>
-      <c r="D61" s="17">
+      <c r="D61" s="14">
         <v>100</v>
       </c>
-      <c r="E61" s="17">
+      <c r="E61" s="14">
         <v>60</v>
       </c>
-      <c r="F61" s="17">
+      <c r="F61" s="14">
         <v>200</v>
       </c>
-      <c r="G61" s="17">
+      <c r="G61" s="14">
         <v>4</v>
       </c>
-      <c r="H61" s="17">
+      <c r="H61" s="14">
         <v>60</v>
       </c>
-      <c r="I61" s="18">
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="J61" s="18">
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K61" s="19" t="s">
+      <c r="K61" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L61" s="19" t="s">
+      <c r="L61" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="M61" s="19" t="s">
+      <c r="M61" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N61" s="20" t="s">
+      <c r="N61" s="17" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="16">
+      <c r="A62" s="13">
         <v>46303</v>
       </c>
-      <c r="B62" s="17">
+      <c r="B62" s="14">
         <v>540</v>
       </c>
-      <c r="C62" s="17">
+      <c r="C62" s="14">
         <v>60</v>
       </c>
-      <c r="D62" s="17">
+      <c r="D62" s="14">
         <v>120</v>
       </c>
-      <c r="E62" s="17">
+      <c r="E62" s="14">
         <v>60</v>
       </c>
-      <c r="F62" s="17">
+      <c r="F62" s="14">
         <v>0</v>
       </c>
-      <c r="G62" s="17">
+      <c r="G62" s="14">
         <v>0</v>
       </c>
-      <c r="H62" s="17">
+      <c r="H62" s="14">
         <v>180</v>
       </c>
-      <c r="I62" s="18">
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="J62" s="18">
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K62" s="19" t="s">
+      <c r="K62" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L62" s="19" t="s">
+      <c r="L62" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M62" s="19" t="s">
+      <c r="M62" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N62" s="20" t="s">
+      <c r="N62" s="17" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="16">
+      <c r="A63" s="13">
         <v>46304</v>
       </c>
-      <c r="B63" s="17">
+      <c r="B63" s="14">
         <v>540</v>
       </c>
-      <c r="C63" s="17">
+      <c r="C63" s="14">
         <v>45</v>
       </c>
-      <c r="D63" s="17">
+      <c r="D63" s="14">
         <v>180</v>
       </c>
-      <c r="E63" s="17">
+      <c r="E63" s="14">
         <v>60</v>
       </c>
-      <c r="F63" s="17">
+      <c r="F63" s="14">
         <v>0</v>
       </c>
-      <c r="G63" s="17">
+      <c r="G63" s="14">
         <v>0</v>
       </c>
-      <c r="H63" s="17">
+      <c r="H63" s="14">
         <v>120</v>
       </c>
-      <c r="I63" s="18">
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
         <v>945</v>
       </c>
-      <c r="J63" s="18">
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
         <v>495</v>
       </c>
-      <c r="K63" s="19" t="s">
+      <c r="K63" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="L63" s="19" t="s">
+      <c r="L63" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M63" s="19" t="s">
+      <c r="M63" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N63" s="20" t="s">
+      <c r="N63" s="17" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="10" t="str">
-        <f t="shared" ref="I6:I69" si="2">IF(SUM(B64:F64,H64)=0,"",SUM(B64:F64,H64))</f>
-        <v/>
-      </c>
-      <c r="J64" s="10" t="str">
-        <f t="shared" ref="J6:J69" si="3">IF(I64="","",1440-I64)</f>
-        <v/>
-      </c>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="12"/>
+      <c r="A64" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B64" s="9">
+        <v>540</v>
+      </c>
+      <c r="C64" s="9">
+        <v>60</v>
+      </c>
+      <c r="D64" s="9">
+        <v>120</v>
+      </c>
+      <c r="E64" s="9">
+        <v>75</v>
+      </c>
+      <c r="F64" s="9">
+        <v>0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>180</v>
+      </c>
+      <c r="I64" s="10">
+        <f t="shared" ref="I64:I69" si="2">IF(SUM(B64:F64,H64)=0,"",SUM(B64:F64,H64))</f>
+        <v>975</v>
+      </c>
+      <c r="J64" s="10">
+        <f t="shared" ref="J64:J69" si="3">IF(I64="","",1440-I64)</f>
+        <v>465</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N64" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="10" t="str">
+      <c r="A65" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B65" s="9">
+        <v>540</v>
+      </c>
+      <c r="C65" s="9">
+        <v>60</v>
+      </c>
+      <c r="D65" s="9">
+        <v>120</v>
+      </c>
+      <c r="E65" s="9">
+        <v>60</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>120</v>
+      </c>
+      <c r="I65" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="str">
+        <v>900</v>
+      </c>
+      <c r="J65" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="12"/>
+        <v>540</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N65" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="10" t="str">
+      <c r="A66" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B66" s="9">
+        <v>540</v>
+      </c>
+      <c r="C66" s="9">
+        <v>120</v>
+      </c>
+      <c r="D66" s="9">
+        <v>180</v>
+      </c>
+      <c r="E66" s="9">
+        <v>65</v>
+      </c>
+      <c r="F66" s="9">
+        <v>0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>120</v>
+      </c>
+      <c r="I66" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J66" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="12"/>
+        <v>415</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>
@@ -11291,12 +11351,7 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J64:J401">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J63">
+  <conditionalFormatting sqref="J6:J401">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
